--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -1,33 +1,97 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>SANTA RITA</t>
+  </si>
+  <si>
+    <t>INDUSTRIA ALIMENTICIA NACIONAL DE CEREALES Y HARINAS C.A</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>Johnny A. Ramos</t>
+  </si>
+  <si>
+    <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+  </si>
+  <si>
+    <t>TIPO C</t>
+  </si>
+  <si>
+    <t>HIST_20260501_0</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +110,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -407,142 +404,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TIPO DE FISCALIZACION</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HIST_20260501_0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SANTA RITA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>INDUSTRIA ALIMENTICIA NACIONAL DE CEREALES Y HARINAS C.A</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
         <v>837608</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Johnny A. Ramos</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TIPO C</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>SKU no pertenece a la recepcion</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2">
         <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -1,97 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>SANTA RITA</t>
-  </si>
-  <si>
-    <t>INDUSTRIA ALIMENTICIA NACIONAL DE CEREALES Y HARINAS C.A</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>Johnny A. Ramos</t>
-  </si>
-  <si>
-    <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
-  </si>
-  <si>
-    <t>TIPO C</t>
-  </si>
-  <si>
-    <t>HIST_20260501_0</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -110,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -404,78 +407,197 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INDUSTRIA ALIMENTICIA NACIONAL DE CEREALES Y HARINAS C.A</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>837608</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Johnny A. Ramos</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>HIST_20260501_0</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2">
-        <v>837608</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>000901</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Daniel j. Blanco</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No termino proceso de fiscalizacion y se elimina la recepcion </t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="s">
-        <v>19</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ID_20260506072345</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>INC_072345.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -1,33 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>FOTO_INCIDENCIA</t>
+  </si>
+  <si>
+    <t>SANTA RITA</t>
+  </si>
+  <si>
+    <t>INDUSTRIA ALIMENTICIA NACIONAL DE CEREALES Y HARINAS C.A</t>
+  </si>
+  <si>
+    <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+  </si>
+  <si>
+    <t>000028040</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>RECEPCION</t>
+  </si>
+  <si>
+    <t>Johnny A. Ramos</t>
+  </si>
+  <si>
+    <t>Daniel j. Blanco</t>
+  </si>
+  <si>
+    <t>Roxana A. Rodriguez</t>
+  </si>
+  <si>
+    <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+  </si>
+  <si>
+    <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+  </si>
+  <si>
+    <t>OTRAS.</t>
+  </si>
+  <si>
+    <t>TIPO C</t>
+  </si>
+  <si>
+    <t>TIPO E</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No termino proceso de fiscalizacion y se elimina la recepcion </t>
+  </si>
+  <si>
+    <t>Se recibe producto Espinaca paq. 200gr, y luego se percata que no esta en orden de compra y regresa a proveedor</t>
+  </si>
+  <si>
+    <t>SIN_FOTO</t>
+  </si>
+  <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
+    <t>HIST_20260501_0</t>
+  </si>
+  <si>
+    <t>ID_20260506072345</t>
+  </si>
+  <si>
+    <t>ID_20260506164605</t>
+  </si>
+  <si>
+    <t>INC_072345.jpg</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +167,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -407,197 +461,166 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>TIPO FISCALIZACIÓN</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>OBSERVACIÓN</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>MONTO $</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACIÓN MONTO</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>FOTO_INCIDENCIA</t>
-        </is>
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SANTA RITA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>INDUSTRIA ALIMENTICIA NACIONAL DE CEREALES Y HARINAS C.A</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
         <v>837608</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Johnny A. Ramos</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>TIPO C</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>HIST_20260501_0</t>
-        </is>
+      <c r="M2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SANTA RITA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>000901</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Daniel j. Blanco</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>TIPO E</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No termino proceso de fiscalizacion y se elimina la recepcion </t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>901</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>SIN_FOTO</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ID_20260506072345</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>INC_072345.jpg</t>
-        </is>
+      <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -1,154 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>FOTO_INCIDENCIA</t>
-  </si>
-  <si>
-    <t>SANTA RITA</t>
-  </si>
-  <si>
-    <t>INDUSTRIA ALIMENTICIA NACIONAL DE CEREALES Y HARINAS C.A</t>
-  </si>
-  <si>
-    <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
-  </si>
-  <si>
-    <t>000028040</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>RECEPCION</t>
-  </si>
-  <si>
-    <t>Johnny A. Ramos</t>
-  </si>
-  <si>
-    <t>Daniel j. Blanco</t>
-  </si>
-  <si>
-    <t>Roxana A. Rodriguez</t>
-  </si>
-  <si>
-    <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
-  </si>
-  <si>
-    <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
-  </si>
-  <si>
-    <t>OTRAS.</t>
-  </si>
-  <si>
-    <t>TIPO C</t>
-  </si>
-  <si>
-    <t>TIPO E</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No termino proceso de fiscalizacion y se elimina la recepcion </t>
-  </si>
-  <si>
-    <t>Se recibe producto Espinaca paq. 200gr, y luego se percata que no esta en orden de compra y regresa a proveedor</t>
-  </si>
-  <si>
-    <t>SIN_FOTO</t>
-  </si>
-  <si>
-    <t>NINGUNA</t>
-  </si>
-  <si>
-    <t>HIST_20260501_0</t>
-  </si>
-  <si>
-    <t>ID_20260506072345</t>
-  </si>
-  <si>
-    <t>ID_20260506164605</t>
-  </si>
-  <si>
-    <t>INC_072345.jpg</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -167,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,166 +407,260 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INDUSTRIA ALIMENTICIA NACIONAL DE CEREALES Y HARINAS C.A</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>837608</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Johnny A. Ramos</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>HIST_20260501_0</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>837608</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>901</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Daniel j. Blanco</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No termino proceso de fiscalizacion y se elimina la recepcion </t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="s">
-        <v>35</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ID_20260506072345</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>INC_072345.jpg</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3">
-        <v>901</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>000028040</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Roxana A. Rodriguez</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Se recibe producto Espinaca paq. 200gr, y luego se percata que no esta en orden de compra y regresa a proveedor</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" t="s">
-        <v>37</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260506164605</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -1,12 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +507,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Johnny A. Ramos</t>
@@ -521,14 +523,18 @@
           <t>TIPO C</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>HIST_20260501_0</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -609,10 +615,8 @@
           <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>000028040</t>
-        </is>
+      <c r="C4" t="n">
+        <v>28040</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -634,11 +638,7 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Se recibe producto Espinaca paq. 200gr, y luego se percata que no esta en orden de compra y regresa a proveedor</t>
@@ -662,8 +662,75 @@
           <t>ID_20260506164605</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MONDELEZ VZ, C.A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>005465141</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yesika A. Ruiz</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Productos pertenecen a otra recepcion</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260507145951</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,8 @@
           <t>MONDELEZ VZ, C.A</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>005465141</t>
-        </is>
+      <c r="C5" t="n">
+        <v>5465141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -729,6 +727,72 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ALIMENTOS HEINZ, C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2226119</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Yesika A. Ruiz</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Productos no pertenecen a la recepcion</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260508094719</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,10 +739,8 @@
           <t>ALIMENTOS HEINZ, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2226119</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2226119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -793,6 +791,392 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SAPORI, C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>131571</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YESIKA A. RUIZ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Error al cargar la documentacion</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260509103517</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>107026</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>YESIKA A. RUIZ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Error al cargar SKU</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260509111831</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INVERSIONES VELANDRIA, C.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7345</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>YESIKA A. RUIZ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>No se indico diferencia al dorso</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ID_20260509111951</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1841</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JOHNNY A. RAMOS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Error al cargar la documentacion</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260511114948</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CORPORACION R3, C.A</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ROXANA A. RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Se realiza la fiscalizacion sin previamente enviar la imagen del documento el cual se iba a recibir</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260511125704</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13650</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JOHNNY A. RAMOS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Falta firma de Gerencia</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260511135328</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -507,7 +507,6 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Johnny A. Ramos</t>
@@ -523,18 +522,14 @@
           <t>TIPO C</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>HIST_20260501_0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -638,7 +633,6 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Se recibe producto Espinaca paq. 200gr, y luego se percata que no esta en orden de compra y regresa a proveedor</t>
@@ -662,7 +656,6 @@
           <t>ID_20260506164605</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -726,7 +719,6 @@
           <t>ID_20260507145951</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -790,7 +782,6 @@
           <t>ID_20260508094719</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -854,7 +845,6 @@
           <t>ID_20260509103517</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -918,7 +908,6 @@
           <t>ID_20260509111831</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -982,7 +971,6 @@
           <t>ID_20260509111951</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1046,7 +1034,6 @@
           <t>ID_20260511114948</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1110,7 +1097,6 @@
           <t>ID_20260511125704</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1176,7 +1162,6 @@
           <t>ID_20260511135328</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Johnny A. Ramos</t>
@@ -522,14 +523,18 @@
           <t>TIPO C</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>HIST_20260501_0</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -633,6 +638,7 @@
           <t>OTRAS.</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Se recibe producto Espinaca paq. 200gr, y luego se percata que no esta en orden de compra y regresa a proveedor</t>
@@ -656,6 +662,7 @@
           <t>ID_20260506164605</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -719,6 +726,7 @@
           <t>ID_20260507145951</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -782,6 +790,7 @@
           <t>ID_20260508094719</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -845,6 +854,7 @@
           <t>ID_20260509103517</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -908,6 +918,7 @@
           <t>ID_20260509111831</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -971,6 +982,7 @@
           <t>ID_20260509111951</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1034,6 +1046,7 @@
           <t>ID_20260511114948</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1097,6 +1110,7 @@
           <t>ID_20260511125704</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1109,10 +1123,8 @@
           <t>ADOLFO'S VICAR, C.A.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>13650</t>
-        </is>
+      <c r="C12" t="n">
+        <v>13650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1162,6 +1174,73 @@
           <t>ID_20260511135328</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BIMBO DE VENEZUELA, C.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0008455722</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JOHNNY A. RAMOS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>No se hizo el envio de la foto al fiscalizador antes de comenzar la recepcion</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ID_20260513113927</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -507,7 +507,6 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Johnny A. Ramos</t>
@@ -523,18 +522,14 @@
           <t>TIPO C</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>HIST_20260501_0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -638,7 +633,6 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Se recibe producto Espinaca paq. 200gr, y luego se percata que no esta en orden de compra y regresa a proveedor</t>
@@ -662,7 +656,6 @@
           <t>ID_20260506164605</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -726,7 +719,6 @@
           <t>ID_20260507145951</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -790,7 +782,6 @@
           <t>ID_20260508094719</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -854,7 +845,6 @@
           <t>ID_20260509103517</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -918,7 +908,6 @@
           <t>ID_20260509111831</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -982,7 +971,6 @@
           <t>ID_20260509111951</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1046,7 +1034,6 @@
           <t>ID_20260511114948</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1110,7 +1097,6 @@
           <t>ID_20260511125704</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1174,7 +1160,6 @@
           <t>ID_20260511135328</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1240,7 +1225,6 @@
           <t>ID_20260513113927</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,8 +498,10 @@
           <t>INDUSTRIA ALIMENTICIA NACIONAL DE CEREALES Y HARINAS C.A</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>837608</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>837608</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,8 +543,10 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>901</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -610,8 +613,10 @@
           <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>28040</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>28040</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -668,8 +673,10 @@
           <t>MONDELEZ VZ, C.A</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>5465141</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5465141</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -731,8 +738,10 @@
           <t>ALIMENTOS HEINZ, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>2226119</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2226119</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -794,8 +803,10 @@
           <t>SAPORI, C.A.</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>131571</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131571</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -857,8 +868,10 @@
           <t>CAVA LUXOR</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>107026</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>107026</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -920,8 +933,10 @@
           <t>INVERSIONES VELANDRIA, C.A.</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>7345</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7345</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -983,8 +998,10 @@
           <t>CAVA LUXOR</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1841</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1841</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1046,8 +1063,10 @@
           <t>CORPORACION R3, C.A</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>2026</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1109,8 +1128,10 @@
           <t>ADOLFO'S VICAR, C.A.</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>13650</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13650</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1226,7 +1247,72 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ITC DISTRIBUCIONES CENTRO C.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>000979618</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ANDRES E. SALAS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SKU DUPLICADO POR ERROR </t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ID_20260515152512</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/SANTA RITA.xlsx
+++ b/cuadros/MAYO/SANTA RITA.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,71 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CENTRAL EL PALMAR, S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>91048838</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>JOHNNY A. RAMOS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Documentacion erronea</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ID_20260515164634</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
